--- a/Tests/excel/module02_test_cases.xlsx
+++ b/Tests/excel/module02_test_cases.xlsx
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống lưu thành công toàn bộ dữ liệu nhận xét cùng một lúc. Hiển thị thông báo lưu thành công (ví dụ: "Saved 2 students"). Dữ liệu hiển thị chính xác trong danh sách.</t>
+          <t>System save successfully toan bo du lieu nhan xet cung mot luc. Hien thi notification save successfully (e.g.: "Saved 2 students"). Du lieu display chinh xac trong danh sach.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>

--- a/Tests/excel/module02_test_cases.xlsx
+++ b/Tests/excel/module02_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module02" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module02" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module02'!$A$1:$N$32</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>System save successfully toan bo du lieu nhan xet cung mot luc. Hien thi notification save successfully (e.g.: "Saved 2 students"). Du lieu display chinh xac trong danh sach.</t>
+          <t>System saves all observation data simultaneously. Success notification appears (e.g.: "Saved 2 students"). Data is displayed accurately in the list.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>

--- a/Tests/excel/module02_test_cases.xlsx
+++ b/Tests/excel/module02_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module02" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module02" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module02'!$A$1:$N$32</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
